--- a/Issues_No_Tests_new.xlsx
+++ b/Issues_No_Tests_new.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,11 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -544,6 +549,31 @@
           <t>Reasoning</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Science Difficulty</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>SWE Difficulty</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>science_relevance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -613,6 +643,31 @@
           <t>The patch directly addresses the reported mechanism by ensuring the CI solver uses the user-specified wavefunction symmetry instead of always guessing it, which should prevent symmetry inconsistency during state-averaged orbital optimization.</t>
         </is>
       </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -682,6 +737,31 @@
           <t>Clamping `r` to at least 1 prevents the problematic NaN-producing regime in the numerical `rcut` estimate for large basis exponents, which the reported decomposition indicates causes incorrect XC energy and SCF non-convergence.</t>
         </is>
       </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -761,6 +841,31 @@
           <t>The reported mechanism is incorrect covariance matrix element ordering affecting eigenvalues; the PR directly changes the computation of the covariance matrix at that location to a consistent covariance calculation, which addresses the mathematical source of the eigenvalue noise, and the adaptive-window behavior is controlled via an opt-out switch as discussed.</t>
         </is>
       </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Earth Science</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -835,6 +940,31 @@
           <t>The PR directly implements the reported numerical-robustness fix by clamping the sqrt radicands to nonnegative values and preventing propagation of NaNs in the loop.</t>
         </is>
       </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Earth Science</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -912,6 +1042,31 @@
           <t>The reported NaN-H mechanism is directly tied to computing the 2D hydrogen placement direction from neighbor vectors, and the PR introduces a specific geometric degeneracy check plus a regression test confirming non-NaN coordinates.</t>
         </is>
       </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -985,6 +1140,31 @@
           <t>Switching to normalized complex Gaussian vectors is the established way to sample Haar-random pure states, directly addressing the reported mismatch in the amplitude distribution.</t>
         </is>
       </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1060,6 +1240,31 @@
           <t>The implementation replaces the TDB-to-pnm06a input with TT at the exact code path in icrs_to_cirs/cirs_to_icrs, aligning with pnm06a’s TT convention and resolving the identified timescale bug.</t>
         </is>
       </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1138,6 +1343,31 @@
           <t>The code changes directly update the parameter-derivative formulas at the reported locations for both Moffat models, aligning them with the corrected calculus described in the issue text.</t>
         </is>
       </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1213,6 +1443,31 @@
           <t>The code change directly corrects the mathematically derived kernel normalization constant for the quartic kernel, aligning the implemented scaling with the provided polar-integration result.</t>
         </is>
       </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Geographical Information Science</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1282,6 +1537,31 @@
           <t>The fix directly addresses the variable initialization defect so CSR normalization can proceed when `exclude_highly_expressed=False` with Numba JIT disabled.</t>
         </is>
       </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1351,6 +1631,31 @@
           <t>The patch directly updates the size normalization to ignore embedding rows that include NaNs, matching matplotlib’s omission behavior and preventing dot sizes from shrinking when NaN-padded cells are present.</t>
         </is>
       </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1431,6 +1736,31 @@
           <t>Using theta directly instead of converting it from degrees to radians makes the rendered rotation consistent with Qiskit’s radian convention, directly fixing the reported mismatch.</t>
         </is>
       </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1504,6 +1834,31 @@
           <t>The PR directly implements requested spherical-coordinate support by applying the standard coordinate transformation before plotting.</t>
         </is>
       </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1577,6 +1932,31 @@
           <t>By adding `CalcRMS`, which performs symmetry-based permutation matching via substructure matches and computes RMSD purely from the existing coordinate frames (no alignment/conformer transform), the PR implements the requested docking-oriented “symmetry matchings and without alignment” capability.</t>
         </is>
       </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1653,6 +2033,31 @@
           <t>The fix directly corrects the wrong UI value feeding the area-threshold parameter, which matches the described symptom that the search results do not correspond to the spinbox value for minimal polygon area.</t>
         </is>
       </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>Geographical Information Science</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1727,6 +2132,31 @@
           <t>The implementation directly updates the rzz decomposition to place the U1 phase on the target qubit rather than the control, which addresses the described incorrect behavior mechanism.</t>
         </is>
       </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1805,6 +2235,31 @@
           <t>By ensuring double precision values like 0.00001 are written and restored with sufficient textual precision and by allowing the UI to accept/display that precision, the fix targets the numerical representation/persistence failure described for the Z Factor.</t>
         </is>
       </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>Geographical Information Science</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1874,6 +2329,31 @@
           <t>The patch changes the membrane bounding-box calculation to be coordinate-correct, which plausibly prevents the zero box dimension that caused the float division by zero in invBox.</t>
         </is>
       </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1951,6 +2431,31 @@
           <t>The code changes in the Padé environment/bath correlation parameter computation remove the incorrect real-part projection and restore correct handling of complex gamma/eta, which is precisely what the issue identifies as causing the shifted Drude-Lorentz mismatch between implementations.</t>
         </is>
       </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2020,6 +2525,31 @@
           <t>The failure reported as outdated center handling is directly addressed by updating partition_index_2d to consistently pass the appropriate center into ds.region and grid_collection.</t>
         </is>
       </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2089,6 +2619,31 @@
           <t>The patch explicitly updates interior-facet RHS assembly to allocate and scatter contributions using the dofmap block size, addressing the mechanism described in the issue.</t>
         </is>
       </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2158,6 +2713,31 @@
           <t>The fix directly changes the overflow-prone quality-summation accumulators from 32-bit int to 64-bit uint64_t in the exact consensus calculation path described, plausibly eliminating the observed high-depth consensus breakage.</t>
         </is>
       </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2227,6 +2807,31 @@
           <t>Changing np.all to np.any in the index-finding logic directly addresses the mechanism that previously missed head movement unless every HPI coil coordinate changed between samples.</t>
         </is>
       </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>Neuroscience</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2300,6 +2905,31 @@
           <t>The code change directly addresses the reported failure mode by ensuring that ONCE chunk IDs are restored from fixstore on subsequent runs rather than triggering unintended recalculation at step 0.</t>
         </is>
       </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2369,6 +2999,31 @@
           <t>The mechanism for the warning is incorrect y-pixel ordering when forming the rectangle pixel bounds, and the PR directly corrects that ordering so the rectangle is no longer misdetected as inverted.</t>
         </is>
       </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2442,6 +3097,31 @@
           <t>By correcting the coord_type used for the wcsaxes grid axes to longitude/latitude when needed, the patch aligns axis semantics with what wcsaxes expects for proper angular tick formatting, plausibly fixing the EIT WCS arcsecond formatting failure described.</t>
         </is>
       </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2523,6 +3203,31 @@
           <t>The PR explicitly updates yt’s symlog colorbar tick/minor-tick and normalization logic with matplotlib 3.5-specific handling, matching the bug’s described colorbar/tick regression mechanism.</t>
         </is>
       </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2603,6 +3308,31 @@
           <t>The fix directly replaces the plain-text 'theta'/'phi' label tokens with LaTeX '\theta'/'\phi' for the spherical 'r' axis label mapping, which matches the requested behavior for SlicePlot spherical data.</t>
         </is>
       </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2682,6 +3412,31 @@
           <t>By converting `radius` to the `center` units at the annotation call site, the implementation aligns radius and center spatial units, addressing the mismatch demonstrated by the base vs expected images.</t>
         </is>
       </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2757,6 +3512,31 @@
           <t>If the user sets zmin&gt;0 and the transform is symlog due to unrelated negative values elsewhere, switching to log_transform ensures the zlim range is respected for the positive-only range.</t>
         </is>
       </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2830,6 +3610,31 @@
           <t>By correcting boundary-time indexing precision and using correct epoch index mapping when drawing, the PR addresses the reported scroll/redraw mismatch where selection and dropped/highlighted epochs become inconsistent.</t>
         </is>
       </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>Neuroscience</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2899,6 +3704,31 @@
           <t>Sampling without replacement directly removes the mechanism that produced identically named design-matrix columns, addressing the random contrast failure.</t>
         </is>
       </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>Neuroscience</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2973,6 +3803,31 @@
           <t>Because the fix changes the colorbar cropping logic to use the correct axis scaling depending on the Matplotlib version, it plausibly restores the intended correspondence between thresholded statmap values and the colorbar range.</t>
         </is>
       </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>Neuroscience</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3046,6 +3901,31 @@
           <t>The change directly addresses the GPU TIP4P virial/pressure computation path that caused the reported pressure offset, so it is a relevant direct fix.</t>
         </is>
       </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3119,6 +3999,31 @@
           <t>The PR modifies the MSM code path responsible for grid allocation and teardown, plausibly fixing the state corruption causing the force accuracy regression.</t>
         </is>
       </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3196,6 +4101,31 @@
           <t>The patch directly targets the affected long-range pair-style write_data/write_coeff path and corrects the per-type-pair cutoff handling that caused the wrong coefficients.</t>
         </is>
       </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3265,6 +4195,31 @@
           <t>The implementation directly targets the reported triclinic/pppm-intel failure mode at the affected code path and plausibly restores correct behavior while preserving orthogonal-cell behavior.</t>
         </is>
       </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3338,6 +4293,31 @@
           <t>This is a domain-specific numerical correctness bug in LAMMPS special-bonds handling, and the code change directly targets the reported hybrid sub-style matching failure.</t>
         </is>
       </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3411,6 +4391,31 @@
           <t>The PR directly modifies the Gay-Berne derivative terms at the reported code path across implementations, plausibly correcting the torque/force calculation responsible for the energy drift.</t>
         </is>
       </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3484,6 +4489,31 @@
           <t>The modified outside() logic directly addresses the reported z-periodic overlap bug in fix_pour by fixing the periodic-boundary inclusion test.</t>
         </is>
       </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3558,6 +4588,31 @@
           <t>The PR directly fixes the PPPM/TIP4P triclinic coordinate handling at the implicated code path, plausibly addressing both the wrong energies and the out-of-range atoms crash.</t>
         </is>
       </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3627,6 +4682,31 @@
           <t>The change directly addresses the reported scientific correctness bug by separating REBO from AIREBO parameterization and wiring REBO to its own parameter file.</t>
         </is>
       </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3701,6 +4781,31 @@
           <t>The code change is localized to the communication path implicated by the bug and plausibly removes the MPI hang/crash cause reported for tiled communications under periodic boundaries.</t>
         </is>
       </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3774,6 +4879,31 @@
           <t>The PR directly states and touches the dump code path implicated by the triclinic `dump_modify pbc` wrapping bug, so it plausibly fixes the reported behavior.</t>
         </is>
       </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3847,6 +4977,31 @@
           <t>The change directly addresses the reported segmentation fault mechanism by handling per-atom masses in the affected scientific compute routines.</t>
         </is>
       </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3916,6 +5071,31 @@
           <t>Adding pyscf/scf/atom_ks.py together with SAD DFT-specific atomic configurations and wiring indicates the PR implements the requested spherically averaged atomic DFT functionality rather than merely suggesting code changes or addressing unrelated aspects.</t>
         </is>
       </c>
+      <c r="T47" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3985,6 +5165,31 @@
           <t>The fix directly addresses the mechanism of the broadcasting error by converting the Huckel atomic orbital coefficients into the same (cartesian) AO representation used for `orb_C` when `mol.cart=True`.</t>
         </is>
       </c>
+      <c r="T48" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4054,6 +5259,31 @@
           <t>The code change adds explicit range-separated detection to the hybrid-classification logic, which plausibly fixes the TDDFT driver mis-selection that occurred for CAM-B3LYP passed as a LibXC keyword.</t>
         </is>
       </c>
+      <c r="T49" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4123,6 +5353,31 @@
           <t>The fix changes both the targeted weight formula and the use-sites to the correct Chebyshev quadrature of the second kind, plausibly resolving the node/weight mismatch described.</t>
         </is>
       </c>
+      <c r="T50" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4192,6 +5447,31 @@
           <t>The diff directly updates the specific variable name so that the stored left eigenvector uses the intended beta slot instead of overwriting the alpha slot.</t>
         </is>
       </c>
+      <c r="T51" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4261,6 +5541,31 @@
           <t>The requested fix is to ensure frozen-core is included in the DF-OCC memory estimation, and the implementation updates the relevant amplitude memory products to use the frozen-core-adjusted occupied dimensions (naocc* rather than nocc2*).</t>
         </is>
       </c>
+      <c r="T52" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4335,6 +5640,31 @@
           <t>The implementation directly applies the requested +1 correction to the mlabday numeric conversion used by array_processing.</t>
         </is>
       </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>Earth Science</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4413,6 +5743,31 @@
           <t>The reported wrong-radius bug is caused by using the polar nominal value where the equatorial nominal value is expected, and the PR directly corrects both the constant and unit equivalence values to 6.3781e6 m.</t>
         </is>
       </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4487,6 +5842,31 @@
           <t>Enabling `prefixes=True` in the unit definitions is the targeted mechanism to make prefixed units like `MBq` available, matching the reported missing-attribute bug.</t>
         </is>
       </c>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4561,6 +5941,31 @@
           <t>The change replaces the Quantity-only `.to_value(cu.redshift)` call with a conversion expression that supports `Column` objects that provide `unit` but not `.to_value`, thereby preventing the reported `AttributeError` and producing redshift values consistently.</t>
         </is>
       </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4634,6 +6039,31 @@
           <t>The code addition introduces the Planck 2018 cosmological parameter values into the core cosmology parameters registry, enabling users to select them as a new named option.</t>
         </is>
       </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4708,6 +6138,31 @@
           <t>The patch directly removes the specific mechanism (propagating overlapping frame attributes) identified as extraneous in StaticMatrixTransform, aligning implementation with the stated bugfix.</t>
         </is>
       </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4781,6 +6236,31 @@
           <t>The implementation directly addresses the reported mechanism (vertical origin/orientation mismatch) by setting the correct origin when writing raster images.</t>
         </is>
       </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4854,6 +6334,31 @@
           <t>The patch replaces the broken internal computation path with the correct sklearn balanced_accuracy_score call using the computed weights, which plausibly restores the metric’s correct behavior.</t>
         </is>
       </c>
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4932,6 +6437,31 @@
           <t>The change implements the intended domain-semantic interpretation that an observation’s phenomenonTime instant (single datetime) should be mapped to a time interval with start=end, avoiding NULLs.</t>
         </is>
       </c>
+      <c r="T61" s="3" t="inlineStr">
+        <is>
+          <t>Geographical Information Science</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5003,6 +6533,31 @@
       <c r="S62" s="3" t="inlineStr">
         <is>
           <t>The change removes in-place assignment during spherical-to-Cartesian conversion, so list inputs are no longer mutated and tuple inputs are supported.</t>
+        </is>
+      </c>
+      <c r="T62" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
@@ -5083,6 +6638,31 @@
           <t>The code change directly implements the exact missing `XXMinusYY` equivalence using the stated RXX/RYY-based decomposition, thereby resolving the feature request.</t>
         </is>
       </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5157,6 +6737,31 @@
           <t>Changing the library’s `sx` definition from `pow(1/2)` to `pow(0.5)` directly addresses the reported integer-division evaluation problem and makes inline behavior match the included standard definition.</t>
         </is>
       </c>
+      <c r="T64" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5232,6 +6837,31 @@
           <t>The reported malfunction is in how density-matrix entries are mapped to Hinton-plot coordinates and how subplot axes/ticks are configured, and the patch directly corrects those coordinate and axis assignments.</t>
         </is>
       </c>
+      <c r="T65" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5301,6 +6931,31 @@
           <t>By switching the palette equality check to np.array_equal, the code avoids numpy-version-dependent behavior that can trigger the reported UFuncTypeError when determining whether an array palette has changed.</t>
         </is>
       </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5380,6 +7035,31 @@
           <t>The code change directly amends the benzyl deprotection SMARTS to include the missing benzylic [CH2] carbon, aligning the reaction substructure match with true benzyl ethers and preventing phenyl ether matches.</t>
         </is>
       </c>
+      <c r="T67" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5453,6 +7133,31 @@
           <t>The patch directly targets the stated offending code path by turning off strict implicit valence calculation in reactions and adds a regression test for the minimal SMARTS example.</t>
         </is>
       </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5526,6 +7231,31 @@
           <t>The PR directly addresses the reported sanitization/halogen cleanup mechanism by preventing erroneous iodine partial positive charge assignment except in the specific double-bond-plus-oxygen-negative-charge case, and it adds regression tests for the problematic and related hypervalent iodine SMILES.</t>
         </is>
       </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5599,6 +7329,31 @@
           <t>By directly inverting the wheel-delta-to-zoom-direction mapping used for wheel-based magnification, the implementation achieves the requested reverse wheel zoom behavior without changing unrelated non-wheel zoom tools.</t>
         </is>
       </c>
+      <c r="T70" s="3" t="inlineStr">
+        <is>
+          <t>Geographical Information Science</t>
+        </is>
+      </c>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5674,6 +7429,31 @@
           <t>The code directly implements optional endpoint zeroing (with amplitude preservation when enabled) for the specified pulse types, matching the requested enhancement.</t>
         </is>
       </c>
+      <c r="T71" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5749,6 +7529,31 @@
       <c r="S72" s="3" t="inlineStr">
         <is>
           <t>By normalizing the phase angle to a strictly nonnegative interval, the vectors’ phase-dependent color no longer hits the black/off-range case caused by negative angles.</t>
+        </is>
+      </c>
+      <c r="T72" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
@@ -5813,6 +7618,31 @@
           <t>The quantum tensor-dimension invariant gives a self-contained reproducer and precise mathematical oracle for random ket generation.</t>
         </is>
       </c>
+      <c r="T73" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5870,6 +7700,31 @@
           <t>The warning originates from a numerical linear-algebra operation (matrix square root / fidelity for PSD density matrices) that should remain well-defined for pure states, so the fix requires domain-algorithmic handling (e.g., spectral decomposition) to avoid singular-matrix warnings while preserving correct fidelity.</t>
         </is>
       </c>
+      <c r="T74" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5931,6 +7786,31 @@
           <t>The bug is caused by the internal defaulting logic when `top_n_markers=None`, leading to an incorrect marker selection or overlap denominator so overlaps become constant across clusters instead of varying with the actually selected marker genes.</t>
         </is>
       </c>
+      <c r="T75" s="3" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5990,6 +7870,31 @@
       <c r="S76" s="3" t="inlineStr">
         <is>
           <t>The bug concerns the mathematical correctness of the analytical gradient of a UFF inversion energy term (sign of the C2 contribution), which is a domain-specific numerical derivative issue.</t>
+        </is>
+      </c>
+      <c r="T76" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
